--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,1175 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126117441</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91686</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608986</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7020696</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126108977</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>609071</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7020613</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126107504</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103396</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>609132</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7020575</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126117432</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608932</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7020727</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126117434</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608945</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7020723</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126117436</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>609068</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7020616</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126117447</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91528</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>609072</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7020624</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126107443</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609131</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7020584</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126107889</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>609111</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7020595</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126117439</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97415</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>609070</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7020606</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126117435</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>609028</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7020631</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126117433</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>608942</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7020720</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B8" t="n">
-        <v>103396</v>
+        <v>100428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R8" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B9" t="n">
-        <v>100428</v>
+        <v>103396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R9" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B8" t="n">
-        <v>100428</v>
+        <v>103396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R8" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B9" t="n">
-        <v>103396</v>
+        <v>100428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R9" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,7 +1146,7 @@
         <v>126117441</v>
       </c>
       <c r="B6" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126108977</v>
       </c>
       <c r="B7" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B8" t="n">
-        <v>103396</v>
+        <v>100430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R8" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B9" t="n">
-        <v>100428</v>
+        <v>103398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R9" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126117434</v>
       </c>
       <c r="B10" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126117436</v>
       </c>
       <c r="B11" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>126107889</v>
       </c>
       <c r="B14" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B15" t="n">
-        <v>97415</v>
+        <v>100430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R15" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B16" t="n">
-        <v>100428</v>
+        <v>97417</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R16" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2218,7 +2218,7 @@
         <v>126117433</v>
       </c>
       <c r="B17" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,6 +2309,103 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126117459</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103398</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>608950</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7020713</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2407,6 +2407,200 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126223452</v>
+      </c>
+      <c r="B19" t="n">
+        <v>41430</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trolldruvemätare</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Baptria tibiale</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Esper, 1790)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>609026</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7020672</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126223327</v>
+      </c>
+      <c r="B20" t="n">
+        <v>41430</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Trolldruvemätare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Baptria tibiale</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Esper, 1790)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>609009</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7020655</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1146,7 +1146,7 @@
         <v>126117441</v>
       </c>
       <c r="B6" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126108977</v>
       </c>
       <c r="B7" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B8" t="n">
-        <v>100430</v>
+        <v>103400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R8" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B9" t="n">
-        <v>103398</v>
+        <v>100432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R9" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126117434</v>
       </c>
       <c r="B10" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126117436</v>
       </c>
       <c r="B11" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>126107889</v>
       </c>
       <c r="B14" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126117435</v>
       </c>
       <c r="B15" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>126117439</v>
       </c>
       <c r="B16" t="n">
-        <v>97417</v>
+        <v>97419</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>126117433</v>
       </c>
       <c r="B17" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126117459</v>
       </c>
       <c r="B18" t="n">
-        <v>103398</v>
+        <v>103400</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,6 +2601,308 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126237637</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>608968</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7020699</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126237636</v>
+      </c>
+      <c r="B22" t="n">
+        <v>41430</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trolldruvemätare</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Baptria tibiale</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Esper, 1790)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>608968</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7020699</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126237638</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100432</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>609052</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7020728</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>126117441</v>
       </c>
       <c r="B6" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126108977</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B8" t="n">
-        <v>103400</v>
+        <v>100434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R8" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B9" t="n">
-        <v>100432</v>
+        <v>103404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R9" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126117434</v>
       </c>
       <c r="B10" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126117436</v>
       </c>
       <c r="B11" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>126107889</v>
       </c>
       <c r="B14" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B15" t="n">
-        <v>100432</v>
+        <v>97421</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R15" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B16" t="n">
-        <v>97419</v>
+        <v>100434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R16" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2218,7 +2218,7 @@
         <v>126117433</v>
       </c>
       <c r="B17" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126117459</v>
       </c>
       <c r="B18" t="n">
-        <v>103400</v>
+        <v>103404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>126237637</v>
       </c>
       <c r="B21" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>126237638</v>
       </c>
       <c r="B23" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B15" t="n">
-        <v>97421</v>
+        <v>100434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R15" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B16" t="n">
-        <v>100434</v>
+        <v>97421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R16" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>126117441</v>
       </c>
       <c r="B6" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126108977</v>
       </c>
       <c r="B7" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B8" t="n">
-        <v>100434</v>
+        <v>103417</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R8" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B9" t="n">
-        <v>103404</v>
+        <v>100438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R9" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126117434</v>
       </c>
       <c r="B10" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126117436</v>
       </c>
       <c r="B11" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>126107889</v>
       </c>
       <c r="B14" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B15" t="n">
-        <v>100434</v>
+        <v>97425</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R15" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B16" t="n">
-        <v>97421</v>
+        <v>100438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R16" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2218,7 +2218,7 @@
         <v>126117433</v>
       </c>
       <c r="B17" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126117459</v>
       </c>
       <c r="B18" t="n">
-        <v>103404</v>
+        <v>103417</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>126237637</v>
       </c>
       <c r="B21" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>126237638</v>
       </c>
       <c r="B23" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126107504</v>
+        <v>126117432</v>
       </c>
       <c r="B8" t="n">
-        <v>103417</v>
+        <v>100441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,16 +1348,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609132</v>
+        <v>608932</v>
       </c>
       <c r="R8" t="n">
-        <v>7020575</v>
+        <v>7020727</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126117432</v>
+        <v>126107504</v>
       </c>
       <c r="B9" t="n">
-        <v>100438</v>
+        <v>103420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>608932</v>
+        <v>609132</v>
       </c>
       <c r="R9" t="n">
-        <v>7020727</v>
+        <v>7020575</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126117434</v>
       </c>
       <c r="B10" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126117436</v>
       </c>
       <c r="B11" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,48 +1725,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117447</v>
+        <v>126107443</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>100441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609072</v>
+        <v>609131</v>
       </c>
       <c r="R12" t="n">
-        <v>7020624</v>
+        <v>7020584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,48 +1827,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126107443</v>
+        <v>126117447</v>
       </c>
       <c r="B13" t="n">
-        <v>100438</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609131</v>
+        <v>609072</v>
       </c>
       <c r="R13" t="n">
-        <v>7020584</v>
+        <v>7020624</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,7 +1927,7 @@
         <v>126107889</v>
       </c>
       <c r="B14" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>126117439</v>
       </c>
       <c r="B15" t="n">
-        <v>97425</v>
+        <v>97428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>126117435</v>
       </c>
       <c r="B16" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>126117433</v>
       </c>
       <c r="B17" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126117459</v>
       </c>
       <c r="B18" t="n">
-        <v>103417</v>
+        <v>103420</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>126237637</v>
       </c>
       <c r="B21" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>126237638</v>
       </c>
       <c r="B23" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1725,48 +1725,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126107443</v>
+        <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>100441</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609131</v>
+        <v>609072</v>
       </c>
       <c r="R12" t="n">
-        <v>7020584</v>
+        <v>7020624</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,48 +1822,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117447</v>
+        <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>100441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609072</v>
+        <v>609131</v>
       </c>
       <c r="R13" t="n">
-        <v>7020624</v>
+        <v>7020584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>126117441</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>126108977</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>126117432</v>
       </c>
       <c r="B8" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>126107504</v>
       </c>
       <c r="B9" t="n">
-        <v>103420</v>
+        <v>103429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>126117434</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>126117436</v>
       </c>
       <c r="B11" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>126107889</v>
       </c>
       <c r="B14" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B15" t="n">
-        <v>97428</v>
+        <v>100450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R15" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B16" t="n">
-        <v>100441</v>
+        <v>97437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R16" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2218,7 +2218,7 @@
         <v>126117433</v>
       </c>
       <c r="B17" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126117459</v>
       </c>
       <c r="B18" t="n">
-        <v>103420</v>
+        <v>103429</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>126223452</v>
       </c>
       <c r="B19" t="n">
-        <v>41430</v>
+        <v>41431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>126223327</v>
       </c>
       <c r="B20" t="n">
-        <v>41430</v>
+        <v>41431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>126237637</v>
       </c>
       <c r="B21" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126237636</v>
       </c>
       <c r="B22" t="n">
-        <v>41430</v>
+        <v>41431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>126237638</v>
       </c>
       <c r="B23" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1725,48 +1725,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126117447</v>
+        <v>126107443</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>100450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609072</v>
+        <v>609131</v>
       </c>
       <c r="R12" t="n">
-        <v>7020624</v>
+        <v>7020584</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,48 +1827,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126107443</v>
+        <v>126117447</v>
       </c>
       <c r="B13" t="n">
-        <v>100450</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609131</v>
+        <v>609072</v>
       </c>
       <c r="R13" t="n">
-        <v>7020584</v>
+        <v>7020624</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B15" t="n">
-        <v>100450</v>
+        <v>97437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R15" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B16" t="n">
-        <v>97437</v>
+        <v>100450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R16" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B15" t="n">
-        <v>97437</v>
+        <v>100450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R15" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B16" t="n">
-        <v>100450</v>
+        <v>97437</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R16" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117435</v>
+        <v>126117439</v>
       </c>
       <c r="B15" t="n">
-        <v>100450</v>
+        <v>97437</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609028</v>
+        <v>609070</v>
       </c>
       <c r="R15" t="n">
-        <v>7020631</v>
+        <v>7020606</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117439</v>
+        <v>126117435</v>
       </c>
       <c r="B16" t="n">
-        <v>97437</v>
+        <v>100450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609070</v>
+        <v>609028</v>
       </c>
       <c r="R16" t="n">
-        <v>7020606</v>
+        <v>7020631</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -1725,48 +1725,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126107443</v>
+        <v>126117447</v>
       </c>
       <c r="B12" t="n">
-        <v>100450</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609131</v>
+        <v>609072</v>
       </c>
       <c r="R12" t="n">
-        <v>7020584</v>
+        <v>7020624</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,48 +1822,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117447</v>
+        <v>126107443</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>100450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609072</v>
+        <v>609131</v>
       </c>
       <c r="R13" t="n">
-        <v>7020624</v>
+        <v>7020584</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1898,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104052363</v>
+        <v>104053072</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608907.6306567638</v>
+        <v>609117</v>
       </c>
       <c r="R2" t="n">
-        <v>7020726.693317582</v>
+        <v>7020588</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,19 +744,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104053072</v>
+        <v>105164648</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,17 +802,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609116.51854532</v>
+        <v>609100</v>
       </c>
       <c r="R3" t="n">
-        <v>7020587.501939664</v>
+        <v>7020577</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +841,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,27 +858,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105164653</v>
+        <v>105164649</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608910.858028671</v>
+        <v>609117</v>
       </c>
       <c r="R4" t="n">
-        <v>7020724.552329816</v>
+        <v>7020586</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,24 +942,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105164649</v>
+        <v>104052970</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,34 +986,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrtannflo värdetrakt, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609117.4647211104</v>
+        <v>609090</v>
       </c>
       <c r="R5" t="n">
-        <v>7020586.18377961</v>
+        <v>7020624</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,19 +1044,9 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,61 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jennifer C. Johansson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126117441</v>
+        <v>105164650</v>
       </c>
       <c r="B6" t="n">
-        <v>91699</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608986</v>
+        <v>609080</v>
       </c>
       <c r="R6" t="n">
-        <v>7020696</v>
+        <v>7020625</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,12 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,22 +1158,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126108977</v>
+        <v>105164652</v>
       </c>
       <c r="B7" t="n">
-        <v>91541</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,28 +1194,28 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609071</v>
+        <v>609074</v>
       </c>
       <c r="R7" t="n">
-        <v>7020613</v>
+        <v>7020634</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,12 +1239,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,60 +1259,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126117432</v>
+        <v>126108977</v>
       </c>
       <c r="B8" t="n">
-        <v>100450</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>608932</v>
+        <v>609071</v>
       </c>
       <c r="R8" t="n">
-        <v>7020727</v>
+        <v>7020613</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,48 +1372,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126107504</v>
+        <v>126117447</v>
       </c>
       <c r="B9" t="n">
-        <v>103429</v>
+        <v>92208</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609132</v>
+        <v>609072</v>
       </c>
       <c r="R9" t="n">
-        <v>7020575</v>
+        <v>7020624</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,45 +1469,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126117434</v>
+        <v>104052973</v>
       </c>
       <c r="B10" t="n">
-        <v>100450</v>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>608945</v>
+        <v>609090</v>
       </c>
       <c r="R10" t="n">
-        <v>7020723</v>
+        <v>7020624</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1596,12 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,45 +1567,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126117436</v>
+        <v>105164651</v>
       </c>
       <c r="B11" t="n">
-        <v>100450</v>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609068</v>
+        <v>609090</v>
       </c>
       <c r="R11" t="n">
-        <v>7020616</v>
+        <v>7020625</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,12 +1632,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,60 +1652,64 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126107443</v>
+        <v>126117441</v>
       </c>
       <c r="B12" t="n">
-        <v>100450</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609131</v>
+        <v>608986</v>
       </c>
       <c r="R12" t="n">
-        <v>7020584</v>
+        <v>7020696</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,11 +1739,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,45 +1765,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126117447</v>
+        <v>126223327</v>
       </c>
       <c r="B13" t="n">
-        <v>91541</v>
+        <v>41670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609072</v>
+        <v>609009</v>
       </c>
       <c r="R13" t="n">
-        <v>7020624</v>
+        <v>7020655</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,12 +1830,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,32 +1862,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126107889</v>
+        <v>126223452</v>
       </c>
       <c r="B14" t="n">
-        <v>100450</v>
+        <v>41670</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>100453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1897,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609111</v>
+        <v>609026</v>
       </c>
       <c r="R14" t="n">
-        <v>7020595</v>
+        <v>7020672</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1989,12 +1927,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,45 +1959,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126117439</v>
+        <v>126237636</v>
       </c>
       <c r="B15" t="n">
-        <v>97437</v>
+        <v>41670</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220250</v>
+        <v>100453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Yttersel, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609070</v>
+        <v>608968</v>
       </c>
       <c r="R15" t="n">
-        <v>7020606</v>
+        <v>7020699</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2086,12 +2029,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,6 +2043,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2118,45 +2062,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126117435</v>
+        <v>104052363</v>
       </c>
       <c r="B16" t="n">
-        <v>100450</v>
+        <v>58114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609028</v>
+        <v>608907</v>
       </c>
       <c r="R16" t="n">
-        <v>7020631</v>
+        <v>7020726</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2183,12 +2133,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2215,45 +2165,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126117433</v>
+        <v>105164653</v>
       </c>
       <c r="B17" t="n">
-        <v>100450</v>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>608942</v>
+        <v>608911</v>
       </c>
       <c r="R17" t="n">
-        <v>7020720</v>
+        <v>7020725</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2280,12 +2230,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2300,22 +2255,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jennifer C. Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126117459</v>
+        <v>126117439</v>
       </c>
       <c r="B18" t="n">
-        <v>103429</v>
+        <v>98186</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,21 +2282,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222395</v>
+        <v>220250</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2306,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>608950</v>
+        <v>609070</v>
       </c>
       <c r="R18" t="n">
-        <v>7020713</v>
+        <v>7020606</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2409,32 +2368,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126223452</v>
+        <v>126107504</v>
       </c>
       <c r="B19" t="n">
-        <v>41431</v>
+        <v>104253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100453</v>
+        <v>222395</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2444,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609026</v>
+        <v>609132</v>
       </c>
       <c r="R19" t="n">
-        <v>7020672</v>
+        <v>7020575</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2474,12 +2433,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2506,45 +2465,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126223327</v>
+        <v>126117459</v>
       </c>
       <c r="B20" t="n">
-        <v>41431</v>
+        <v>104253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100453</v>
+        <v>222395</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609009</v>
+        <v>608950</v>
       </c>
       <c r="R20" t="n">
-        <v>7020655</v>
+        <v>7020713</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2571,12 +2530,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2603,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126237637</v>
+        <v>126107332</v>
       </c>
       <c r="B21" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,17 +2593,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Yttersel, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>608968</v>
+        <v>609117</v>
       </c>
       <c r="R21" t="n">
-        <v>7020699</v>
+        <v>7020573</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2668,12 +2627,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2700,53 +2659,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126237636</v>
+        <v>126107443</v>
       </c>
       <c r="B22" t="n">
-        <v>41431</v>
+        <v>101228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100453</v>
+        <v>222771</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trolldruvemätare</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Baptria tibiale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Esper, 1790)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Yttersel, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>608968</v>
+        <v>609131</v>
       </c>
       <c r="R22" t="n">
-        <v>7020699</v>
+        <v>7020584</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2770,12 +2724,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2784,7 +2743,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2803,10 +2761,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126237638</v>
+        <v>126107889</v>
       </c>
       <c r="B23" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2832,23 +2790,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Yttersel, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609052</v>
+        <v>609111</v>
       </c>
       <c r="R23" t="n">
-        <v>7020728</v>
+        <v>7020595</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2872,12 +2826,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2886,7 +2840,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2902,6 +2855,787 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126117432</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>608932</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7020727</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126117433</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>608942</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7020720</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126117434</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>608945</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7020723</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126117435</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>609028</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7020631</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126117436</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>609068</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7020616</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126117438</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609068</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7020601</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126237637</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>608968</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7020699</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126237638</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yttersel, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>609052</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7020728</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25941-2025 artfynd.xlsx
+++ b/artfynd/A 25941-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104053072</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164648</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052970</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126108977</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117447</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052973</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164651</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117441</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126223327</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126223452</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2059,6 +2129,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237636</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052363</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164653</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2365,6 +2450,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117439</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2462,6 +2552,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126107504</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2559,6 +2654,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117459</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2656,6 +2756,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126107332</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2758,6 +2863,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126107443</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2855,6 +2965,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126107889</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2952,6 +3067,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117432</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3049,6 +3169,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117433</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3146,6 +3271,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117434</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3243,6 +3373,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117435</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3340,6 +3475,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117436</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3437,6 +3577,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126117438</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3534,6 +3679,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237637</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3636,8 +3786,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126237638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>